--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 03:28:45 UTC</t>
+          <t>2026-08-05 03:51:30 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.45</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 03:51:30 UTC</t>
+          <t>2026-08-05 04:09:35 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.46</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 04:09:35 UTC</t>
+          <t>2026-08-05 05:18:43 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.28</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 05:18:43 UTC</t>
+          <t>2026-08-06 05:20:10 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.44</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06 05:20:10 UTC</t>
+          <t>2026-08-07 04:30:29 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.43</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 04:30:29 UTC</t>
+          <t>2026-08-08 03:29:10 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.39</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08 03:29:10 UTC</t>
+          <t>2026-08-09 03:44:59 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.54</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 03:44:59 UTC</t>
+          <t>2026-08-10 03:56:45 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.50</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 03:56:45 UTC</t>
+          <t>2026-08-11 03:46:41 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>20.36</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 03:46:41 UTC</t>
+          <t>2026-08-12 04:10:36 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.32</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 04:10:36 UTC</t>
+          <t>2026-08-13 04:16:24 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.46</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 04:16:24 UTC</t>
+          <t>2026-08-14 04:11:54 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.36</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 04:11:54 UTC</t>
+          <t>2026-08-15 02:55:04 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.72</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 02:55:04 UTC</t>
+          <t>2026-08-16 03:03:53 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.33</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16 03:03:53 UTC</t>
+          <t>2026-08-17 03:02:42 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.54</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 03:02:42 UTC</t>
+          <t>2026-08-18 02:59:38 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>21.10</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18 02:59:38 UTC</t>
+          <t>2026-08-19 03:00:56 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>20.31</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 03:00:56 UTC</t>
+          <t>2026-08-20 03:00:00 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.40</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 03:00:00 UTC</t>
+          <t>2026-08-21 03:05:36 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.40</t>
+          <t>20.28</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21 03:05:36 UTC</t>
+          <t>2026-08-22 02:57:31 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.38</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22 02:57:31 UTC</t>
+          <t>2026-08-23 03:05:03 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.46</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23 03:05:03 UTC</t>
+          <t>2026-08-24 03:05:46 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.32</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 03:05:46 UTC</t>
+          <t>2026-08-25 03:01:14 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.42</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:01:14 UTC</t>
+          <t>2026-08-26 03:07:50 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.29</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 03:07:50 UTC</t>
+          <t>2026-08-27 12:26:46 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.45</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 12:26:46 UTC</t>
+          <t>2026-08-28 13:51:56 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.32</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 13:51:56 UTC</t>
+          <t>2026-08-29 08:42:15 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.38</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 08:42:15 UTC</t>
+          <t>2026-08-30 07:57:25 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.47</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30 07:57:25 UTC</t>
+          <t>2026-08-31 08:11:45 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.55</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31 08:11:45 UTC</t>
+          <t>2026-09-01 07:21:29 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.32</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 07:21:29 UTC</t>
+          <t>2026-09-02 06:53:35 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.45</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 06:53:35 UTC</t>
+          <t>2026-09-03 06:56:05 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.32</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 06:56:05 UTC</t>
+          <t>2026-09-04 07:00:52 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.30</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 07:00:52 UTC</t>
+          <t>2026-09-05 06:45:26 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.40</t>
         </is>
       </c>
     </row>
